--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>131180100</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104036148</v>
+        <v>104036146</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Acksjön nv, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473161.6447078055</v>
+        <v>473164</v>
       </c>
       <c r="R2" t="n">
-        <v>7012020.598693262</v>
+        <v>7012023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,24 +743,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104036146</v>
+        <v>104036147</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473163.4650242138</v>
+        <v>473180</v>
       </c>
       <c r="R3" t="n">
-        <v>7012022.386510338</v>
+        <v>7012024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +840,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,16 +872,11 @@
         <v>104036155</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473157.4749617097</v>
+        <v>473157</v>
       </c>
       <c r="R4" t="n">
-        <v>7011953.472057806</v>
+        <v>7011953</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +937,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104036147</v>
+        <v>104036154</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473180.6267025439</v>
+        <v>473080</v>
       </c>
       <c r="R5" t="n">
-        <v>7012023.595928025</v>
+        <v>7011900</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,19 +1034,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104036150</v>
+        <v>104036148</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1096,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473182.5589655947</v>
+        <v>473161</v>
       </c>
       <c r="R6" t="n">
-        <v>7012201.618104194</v>
+        <v>7012020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1139,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1264,12 +1176,7 @@
         <v>104036149</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473182.581973678</v>
+        <v>473182</v>
       </c>
       <c r="R7" t="n">
-        <v>7012041.609299188</v>
+        <v>7012042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,19 +1249,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1386,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131180100</v>
+        <v>104036150</v>
       </c>
       <c r="B8" t="n">
-        <v>91824</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,37 +1294,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Acksjön, Jmt</t>
+          <t>Acksjön nv, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473246</v>
+        <v>473182</v>
       </c>
       <c r="R8" t="n">
-        <v>7012290</v>
+        <v>7012202</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,12 +1356,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-06-13</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-06-13</t>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,19 +1381,15 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30068-2022 artfynd.xlsx
+++ b/artfynd/A 30068-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036146</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036154</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036148</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036149</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,8 +1425,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>